--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -492,22 +497,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6562.887</v>
+        <v>6562.893</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4392</v>
+        <v>3.68</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8004</v>
+        <v>-19.15</v>
       </c>
       <c r="H2" t="n">
-        <v>1.086</v>
+        <v>0.8008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9326</v>
+        <v>1.076</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.924</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +535,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6562.914</v>
+        <v>6562.896</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5e-05</v>
+        <v>1.3e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6448</v>
+        <v>3.82</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8252</v>
+        <v>-20.05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.012</v>
+        <v>0.7941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9162</v>
+        <v>1.066</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9095</v>
       </c>
     </row>
     <row r="4">
@@ -562,22 +573,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6562.95</v>
+        <v>6562.956</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2895</v>
+        <v>6.57</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8122</v>
+        <v>-19.43</v>
       </c>
       <c r="H4" t="n">
-        <v>1.116</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9689</v>
+        <v>1.105</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9581</v>
       </c>
     </row>
     <row r="5">
@@ -597,22 +611,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6562.976</v>
+        <v>6562.994</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5e-05</v>
+        <v>2.8e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4873</v>
+        <v>8.33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9569</v>
+        <v>-18.26</v>
       </c>
       <c r="H5" t="n">
-        <v>1.091</v>
+        <v>0.8317</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1354</v>
+        <v>1.056</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9479</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +649,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6563.01</v>
+        <v>6562.991</v>
       </c>
       <c r="E6" t="n">
-        <v>3e-05</v>
+        <v>2.7e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>9.0672</v>
+        <v>8.18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8492</v>
+        <v>-19.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.051</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9826</v>
+        <v>1.082</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.951</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +687,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6563.018</v>
+        <v>6563.03</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.424099999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8949</v>
+        <v>-18.24</v>
       </c>
       <c r="H7" t="n">
-        <v>1.088</v>
+        <v>0.8247</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0641</v>
+        <v>1.064</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9523</v>
       </c>
     </row>
     <row r="8">
@@ -708,16 +731,19 @@
         <v>3.7e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>11.1889</v>
+        <v>11.19</v>
       </c>
       <c r="G8" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.7705</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1.039</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.8619</v>
+      <c r="J8" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="9">
@@ -737,22 +763,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6563.027</v>
+        <v>6563.047</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>9.8093</v>
+        <v>10.74</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8389</v>
+        <v>-18.73</v>
       </c>
       <c r="H9" t="n">
-        <v>1.093</v>
+        <v>0.8136</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9274</v>
       </c>
     </row>
     <row r="10">
@@ -772,22 +801,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6563.024</v>
+        <v>6563.041</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>9.6805</v>
+        <v>10.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8195</v>
+        <v>-18.91</v>
       </c>
       <c r="H10" t="n">
-        <v>1.109</v>
+        <v>0.7994</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9785</v>
+        <v>1.076</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9251</v>
       </c>
     </row>
     <row r="11">
@@ -807,22 +839,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6562.816</v>
+        <v>6562.867</v>
       </c>
       <c r="E11" t="n">
-        <v>1e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1636</v>
+        <v>2.51</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0344</v>
+        <v>-23.73</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.478</v>
+        <v>1.186</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.2452</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
@@ -499,8 +499,10 @@
       <c r="D2" t="n">
         <v>6562.893</v>
       </c>
-      <c r="E2" t="n">
-        <v>1.2e-05</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.2e-05</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>3.68</v>
@@ -509,13 +511,13 @@
         <v>-19.15</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8008</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.924</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="3">
@@ -537,8 +539,10 @@
       <c r="D3" t="n">
         <v>6562.896</v>
       </c>
-      <c r="E3" t="n">
-        <v>1.3e-05</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.3e-05</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>3.82</v>
@@ -547,13 +551,13 @@
         <v>-20.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7941</v>
+        <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>1.066</v>
+        <v>1.07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9095</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="4">
@@ -575,8 +579,10 @@
       <c r="D4" t="n">
         <v>6562.956</v>
       </c>
-      <c r="E4" t="n">
-        <v>2.2e-05</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.2e-05</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>6.57</v>
@@ -585,13 +591,13 @@
         <v>-19.43</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.105</v>
+        <v>1.11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9581</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="5">
@@ -613,8 +619,10 @@
       <c r="D5" t="n">
         <v>6562.994</v>
       </c>
-      <c r="E5" t="n">
-        <v>2.8e-05</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2.8e-05</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>8.33</v>
@@ -623,13 +631,13 @@
         <v>-18.26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8317</v>
+        <v>0.83</v>
       </c>
       <c r="I5" t="n">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9479</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -651,8 +659,10 @@
       <c r="D6" t="n">
         <v>6562.991</v>
       </c>
-      <c r="E6" t="n">
-        <v>2.7e-05</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2.7e-05</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>8.18</v>
@@ -661,13 +671,13 @@
         <v>-19.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.082</v>
+        <v>1.08</v>
       </c>
       <c r="J6" t="n">
-        <v>0.951</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">
@@ -689,8 +699,10 @@
       <c r="D7" t="n">
         <v>6563.03</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.3e-05</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.3e-05</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>9.949999999999999</v>
@@ -699,13 +711,13 @@
         <v>-18.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8247</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.064</v>
+        <v>1.06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9523</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8">
@@ -727,8 +739,10 @@
       <c r="D8" t="n">
         <v>6563.057</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.7e-05</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.7e-05</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>11.19</v>
@@ -737,13 +751,13 @@
         <v>-18.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7705</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>1.039</v>
+        <v>1.04</v>
       </c>
       <c r="J8" t="n">
-        <v>0.862</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="9">
@@ -765,8 +779,10 @@
       <c r="D9" t="n">
         <v>6563.047</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.6e-05</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.6e-05</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>10.74</v>
@@ -775,13 +791,13 @@
         <v>-18.73</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8136</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>1.06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9274</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -803,8 +819,10 @@
       <c r="D10" t="n">
         <v>6563.041</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.5e-05</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>10.45</v>
@@ -813,13 +831,13 @@
         <v>-18.91</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7994</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9251</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="11">
@@ -841,8 +859,10 @@
       <c r="D11" t="n">
         <v>6562.867</v>
       </c>
-      <c r="E11" t="n">
-        <v>8e-06</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8.4e-06</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>2.51</v>
@@ -851,13 +871,13 @@
         <v>-23.73</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="I11" t="n">
-        <v>1.186</v>
+        <v>1.19</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2452</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,41 +843,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Septiembre 21-2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6562.984</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2.6e-05</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-20.45</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Agosto 05-2019</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Hα</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>6562.867</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8.4e-06</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-23.73</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.25</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6562.895</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.3e-05</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6562.907</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-22.08</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
